--- a/instance/uploads/5_dashboard.xlsx
+++ b/instance/uploads/5_dashboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Tito Adriano - Apple/PROJECT DATA WAREHOUSE MAITO/modelo_bd/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Tito Adriano - Apple/PROJECT DATA WAREHOUSE MAITO/bds/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890FB906-AAB2-174E-915C-ED7B6BAD192E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C474721A-706B-8545-8C9F-EA17B81DBE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="500" windowWidth="28240" windowHeight="16840" xr2:uid="{E6384FE7-421F-7B4D-9709-5BB11073D858}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>municipios</t>
   </si>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t>Nharea</t>
-  </si>
-  <si>
-    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -948,6 +945,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="31.5" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -1087,12 +1087,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="1">
-        <v>19082</v>
-      </c>
+      <c r="B11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
